--- a/AAII_Financials/Yearly/CRVO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CRVO_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/CRVO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CRVO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
   <si>
     <t>CRVO</t>
   </si>
@@ -656,81 +656,87 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="D8" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -755,9 +761,12 @@
       <c r="J9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -782,9 +791,12 @@
       <c r="J10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -796,35 +808,39 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E12" s="3">
         <v>7200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>9400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7300</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -849,44 +865,50 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>8600</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>6900</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
@@ -901,11 +923,14 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -914,62 +939,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E17" s="3">
         <v>16000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>19000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18400</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-24700</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-16000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-11600</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-19000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-11300</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K18" s="3">
         <v>-18400</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -981,35 +1013,39 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="3">
-        <v>100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>8900</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="D20" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1034,9 +1070,12 @@
       <c r="J21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1061,63 +1100,72 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-15600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-24500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-15900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-11500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-18800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-18400</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-400</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1142,63 +1190,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-15600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-24100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-14200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-11800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-18800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-18000</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-15600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-24100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-16100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-11800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-27000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-18000</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1223,9 +1280,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1241,18 +1301,21 @@
       <c r="G29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I29" s="3">
         <v>400</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>1100</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1277,9 +1340,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1304,63 +1370,72 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-8900</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="D32" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-15600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-24100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-16100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-11800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-26600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-18000</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1385,68 +1460,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-15600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-24100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-16100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-11800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-26600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-18000</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1458,8 +1542,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1471,44 +1556,48 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E41" s="3">
         <v>10100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>37300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>14200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1600</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E42" s="3">
         <v>12400</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F42" s="3" t="s">
         <v>4</v>
       </c>
@@ -1524,36 +1613,42 @@
       <c r="J42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+        <v>900</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1578,63 +1673,72 @@
       <c r="J44" s="3">
         <v>0</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K44" s="3">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E45" s="3">
         <v>100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E46" s="3">
         <v>22600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>37800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1600</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1659,47 +1763,53 @@
       <c r="J47" s="3">
         <v>0</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E48" s="3">
-        <v>0</v>
+      <c r="E48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F48" s="3">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3">
         <v>300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>100</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
+      <c r="E49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F49" s="3">
-        <v>8600</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3">
         <v>8600</v>
@@ -1708,14 +1818,17 @@
         <v>8600</v>
       </c>
       <c r="I49" s="3">
-        <v>15600</v>
+        <v>8600</v>
       </c>
       <c r="J49" s="3">
         <v>15600</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K49" s="3">
+        <v>15600</v>
+      </c>
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1740,9 +1853,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1767,9 +1883,12 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -1783,20 +1902,23 @@
         <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
         <v>300</v>
       </c>
       <c r="I52" s="3">
+        <v>300</v>
+      </c>
+      <c r="J52" s="3">
         <v>500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>200</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1821,36 +1943,42 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E54" s="3">
         <v>22600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>37800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>24100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>26100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17500</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1862,8 +1990,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1875,40 +2004,44 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1700</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>4</v>
+      <c r="D58" s="3">
+        <v>0</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>4</v>
@@ -1919,72 +2052,81 @@
       <c r="G58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
+      <c r="H58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1900</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>900</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E60" s="3">
         <v>2400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4400</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2007,38 +2149,44 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>600</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
         <v>500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3300</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2063,9 +2211,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2090,9 +2241,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2117,36 +2271,42 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2400</v>
-      </c>
-      <c r="E66" s="3">
-        <v>2900</v>
       </c>
       <c r="F66" s="3">
         <v>2900</v>
       </c>
       <c r="G66" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H66" s="3">
         <v>4000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8300</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2158,8 +2318,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2184,9 +2345,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2211,9 +2375,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2238,9 +2405,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2265,36 +2435,42 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-54400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-145600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-130000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-105900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-91700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-79900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-61600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-60200</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2319,9 +2495,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2346,9 +2525,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2373,36 +2555,42 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E76" s="3">
         <v>20200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>34900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>24800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>21200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9200</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2427,68 +2615,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-15600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-24100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-16100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-11800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-26600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-18000</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2500,16 +2697,17 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
@@ -2524,11 +2722,14 @@
         <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2553,9 +2754,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2580,9 +2784,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2607,9 +2814,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2634,9 +2844,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2661,36 +2874,42 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-15000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-14500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-10800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-12300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-10800</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2702,8 +2921,9 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -2719,18 +2939,21 @@
       <c r="G91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2755,9 +2978,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2782,36 +3008,42 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12200</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>4</v>
+      <c r="F94" s="3">
+        <v>0</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>8500</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2823,8 +3055,9 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -2849,9 +3082,12 @@
       <c r="J96" s="3">
         <v>0</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -2876,9 +3112,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -2903,9 +3142,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -2930,36 +3172,42 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>11100</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>33300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>17900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>16000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>9900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>20100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1800</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -2984,34 +3232,40 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-27200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>18800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-400</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CRVO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CRVO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
   <si>
     <t>CRVO</t>
   </si>
@@ -662,7 +662,9 @@
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -689,17 +691,17 @@
       <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
-        <v>44196</v>
-      </c>
-      <c r="H7" s="2">
-        <v>43830</v>
-      </c>
-      <c r="I7" s="2">
-        <v>43465</v>
-      </c>
-      <c r="J7" s="2">
-        <v>43100</v>
+      <c r="G7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K7" s="2">
         <v>42735</v>
@@ -740,11 +742,11 @@
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
+      <c r="D9" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1300</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>4</v>
@@ -770,11 +772,11 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-1300</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>4</v>
@@ -818,22 +820,22 @@
         <v>8400</v>
       </c>
       <c r="E12" s="3">
-        <v>7200</v>
+        <v>1300</v>
       </c>
       <c r="F12" s="3">
-        <v>8500</v>
-      </c>
-      <c r="G12" s="3">
-        <v>9400</v>
-      </c>
-      <c r="H12" s="3">
-        <v>6600</v>
-      </c>
-      <c r="I12" s="3">
-        <v>5800</v>
-      </c>
-      <c r="J12" s="3">
-        <v>5100</v>
+        <v>2400</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K12" s="3">
         <v>7300</v>
@@ -877,20 +879,20 @@
       <c r="D14" s="3">
         <v>800</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F14" s="3">
-        <v>8600</v>
+        <v>-100</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>6900</v>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
@@ -904,26 +906,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>4</v>
+      <c r="D15" s="3">
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -946,25 +948,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>15000</v>
+        <v>14200</v>
       </c>
       <c r="E17" s="3">
-        <v>16000</v>
+        <v>3500</v>
       </c>
       <c r="F17" s="3">
-        <v>24700</v>
-      </c>
-      <c r="G17" s="3">
-        <v>16000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>11600</v>
-      </c>
-      <c r="I17" s="3">
-        <v>19000</v>
-      </c>
-      <c r="J17" s="3">
-        <v>11300</v>
+        <v>5000</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K17" s="3">
         <v>18400</v>
@@ -976,13 +978,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>4</v>
+        <v>-7000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-5000</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>4</v>
@@ -1020,13 +1022,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>5600</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
+        <v>-5400</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-700</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>4</v>
@@ -1049,26 +1051,26 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
@@ -1079,8 +1081,8 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -1088,17 +1090,17 @@
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1113,22 +1115,22 @@
         <v>-2200</v>
       </c>
       <c r="E23" s="3">
-        <v>-15600</v>
+        <v>-5800</v>
       </c>
       <c r="F23" s="3">
-        <v>-24500</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-15900</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-11500</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-18800</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-2400</v>
+        <v>-4100</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K23" s="3">
         <v>-18400</v>
@@ -1142,23 +1144,23 @@
       <c r="D24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H24" s="3">
-        <v>300</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>-400</v>
@@ -1203,22 +1205,22 @@
         <v>-2200</v>
       </c>
       <c r="E26" s="3">
-        <v>-15600</v>
+        <v>-5800</v>
       </c>
       <c r="F26" s="3">
-        <v>-24100</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-14200</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-11800</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-18800</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-2500</v>
+        <v>-4100</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K26" s="3">
         <v>-18000</v>
@@ -1233,22 +1235,22 @@
         <v>-2200</v>
       </c>
       <c r="E27" s="3">
-        <v>-15600</v>
+        <v>-5800</v>
       </c>
       <c r="F27" s="3">
-        <v>-24100</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-16100</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-11800</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-27000</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-3700</v>
+        <v>-4100</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K27" s="3">
         <v>-18000</v>
@@ -1289,26 +1291,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>4</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>4</v>
@@ -1380,13 +1382,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
+        <v>5400</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F32" s="3">
+        <v>700</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>4</v>
@@ -1413,22 +1415,22 @@
         <v>-2200</v>
       </c>
       <c r="E33" s="3">
-        <v>-15600</v>
+        <v>-5800</v>
       </c>
       <c r="F33" s="3">
-        <v>-24100</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-16100</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-11800</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-26600</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-2600</v>
+        <v>-4100</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K33" s="3">
         <v>-18000</v>
@@ -1473,22 +1475,22 @@
         <v>-2200</v>
       </c>
       <c r="E35" s="3">
-        <v>-15600</v>
+        <v>-5800</v>
       </c>
       <c r="F35" s="3">
-        <v>-24100</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-16100</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-11800</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-26600</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-2600</v>
+        <v>-4100</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K35" s="3">
         <v>-18000</v>
@@ -1513,17 +1515,17 @@
       <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
-        <v>44196</v>
-      </c>
-      <c r="H38" s="2">
-        <v>43830</v>
-      </c>
-      <c r="I38" s="2">
-        <v>43465</v>
-      </c>
-      <c r="J38" s="2">
-        <v>43100</v>
+      <c r="G38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K38" s="2">
         <v>42735</v>
@@ -1566,22 +1568,22 @@
         <v>7800</v>
       </c>
       <c r="E41" s="3">
-        <v>10100</v>
+        <v>4100</v>
       </c>
       <c r="F41" s="3">
-        <v>37300</v>
-      </c>
-      <c r="G41" s="3">
-        <v>18500</v>
-      </c>
-      <c r="H41" s="3">
-        <v>14200</v>
-      </c>
-      <c r="I41" s="3">
-        <v>8000</v>
-      </c>
-      <c r="J41" s="3">
-        <v>8900</v>
+        <v>6700</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K41" s="3">
         <v>1600</v>
@@ -1592,26 +1594,26 @@
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>4</v>
+      <c r="D42" s="3">
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>12400</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>4</v>
@@ -1628,8 +1630,8 @@
       <c r="E43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
+      <c r="F43" s="3">
+        <v>100</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>4</v>
@@ -1652,26 +1654,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1682,26 +1684,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
-        <v>500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>900</v>
-      </c>
-      <c r="J45" s="3">
-        <v>800</v>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K45" s="3">
         <v>100</v>
@@ -1716,22 +1718,22 @@
         <v>10000</v>
       </c>
       <c r="E46" s="3">
-        <v>22600</v>
+        <v>4200</v>
       </c>
       <c r="F46" s="3">
-        <v>37800</v>
-      </c>
-      <c r="G46" s="3">
-        <v>18800</v>
-      </c>
-      <c r="H46" s="3">
-        <v>14600</v>
-      </c>
-      <c r="I46" s="3">
-        <v>8900</v>
-      </c>
-      <c r="J46" s="3">
-        <v>9700</v>
+        <v>6800</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K46" s="3">
         <v>1600</v>
@@ -1742,26 +1744,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -1778,20 +1780,20 @@
       <c r="E48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>300</v>
-      </c>
-      <c r="H48" s="3">
-        <v>500</v>
-      </c>
-      <c r="I48" s="3">
-        <v>400</v>
-      </c>
-      <c r="J48" s="3">
-        <v>500</v>
+      <c r="F48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K48" s="3">
         <v>100</v>
@@ -1802,26 +1804,26 @@
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>4</v>
+      <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
-      <c r="G49" s="3">
-        <v>8600</v>
-      </c>
-      <c r="H49" s="3">
-        <v>8600</v>
-      </c>
-      <c r="I49" s="3">
-        <v>8600</v>
-      </c>
-      <c r="J49" s="3">
-        <v>15600</v>
+      <c r="G49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K49" s="3">
         <v>15600</v>
@@ -1895,23 +1897,23 @@
       <c r="D52" s="3">
         <v>0</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>500</v>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K52" s="3">
         <v>200</v>
@@ -1956,22 +1958,22 @@
         <v>10000</v>
       </c>
       <c r="E54" s="3">
-        <v>22600</v>
+        <v>4200</v>
       </c>
       <c r="F54" s="3">
-        <v>37800</v>
-      </c>
-      <c r="G54" s="3">
-        <v>27700</v>
-      </c>
-      <c r="H54" s="3">
-        <v>24100</v>
-      </c>
-      <c r="I54" s="3">
-        <v>18200</v>
-      </c>
-      <c r="J54" s="3">
-        <v>26100</v>
+        <v>6800</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K54" s="3">
         <v>17500</v>
@@ -2014,22 +2016,22 @@
         <v>700</v>
       </c>
       <c r="E57" s="3">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="F57" s="3">
-        <v>900</v>
-      </c>
-      <c r="G57" s="3">
-        <v>500</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I57" s="3">
-        <v>200</v>
-      </c>
-      <c r="J57" s="3">
-        <v>500</v>
+        <v>0</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K57" s="3">
         <v>1700</v>
@@ -2043,11 +2045,11 @@
       <c r="D58" s="3">
         <v>0</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
+      <c r="E58" s="3">
+        <v>12400</v>
+      </c>
+      <c r="F58" s="3">
+        <v>4100</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>4</v>
@@ -2055,11 +2057,11 @@
       <c r="H58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>600</v>
+      <c r="I58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K58" s="3">
         <v>1900</v>
@@ -2071,25 +2073,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1900</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
-        <v>1300</v>
+        <v>100</v>
       </c>
       <c r="F59" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1900</v>
-      </c>
-      <c r="H59" s="3">
-        <v>500</v>
-      </c>
-      <c r="I59" s="3">
-        <v>600</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1600</v>
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K59" s="3">
         <v>900</v>
@@ -2104,22 +2106,22 @@
         <v>2600</v>
       </c>
       <c r="E60" s="3">
-        <v>2400</v>
+        <v>13200</v>
       </c>
       <c r="F60" s="3">
-        <v>2900</v>
-      </c>
-      <c r="G60" s="3">
-        <v>2400</v>
-      </c>
-      <c r="H60" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I60" s="3">
-        <v>800</v>
-      </c>
-      <c r="J60" s="3">
-        <v>2700</v>
+        <v>4600</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K60" s="3">
         <v>4400</v>
@@ -2137,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2166,20 +2168,20 @@
       <c r="E62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>500</v>
-      </c>
-      <c r="H62" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I62" s="3">
-        <v>1800</v>
-      </c>
-      <c r="J62" s="3">
-        <v>2200</v>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K62" s="3">
         <v>3300</v>
@@ -2284,22 +2286,22 @@
         <v>2600</v>
       </c>
       <c r="E66" s="3">
-        <v>2400</v>
+        <v>13200</v>
       </c>
       <c r="F66" s="3">
-        <v>2900</v>
-      </c>
-      <c r="G66" s="3">
-        <v>2900</v>
-      </c>
-      <c r="H66" s="3">
-        <v>4000</v>
-      </c>
-      <c r="I66" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J66" s="3">
-        <v>4900</v>
+        <v>10500</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K66" s="3">
         <v>8300</v>
@@ -2388,10 +2390,10 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
-        <v>0</v>
+        <v>24300</v>
       </c>
       <c r="F70" s="3">
-        <v>0</v>
+        <v>24300</v>
       </c>
       <c r="G70" s="3">
         <v>0</v>
@@ -2448,22 +2450,22 @@
         <v>-54400</v>
       </c>
       <c r="E72" s="3">
-        <v>-145600</v>
+        <v>-52300</v>
       </c>
       <c r="F72" s="3">
-        <v>-130000</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-105900</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-91700</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-79900</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-61600</v>
+        <v>-46500</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K72" s="3">
         <v>-60200</v>
@@ -2568,22 +2570,22 @@
         <v>7400</v>
       </c>
       <c r="E76" s="3">
-        <v>20200</v>
+        <v>-33300</v>
       </c>
       <c r="F76" s="3">
-        <v>34900</v>
-      </c>
-      <c r="G76" s="3">
-        <v>24800</v>
-      </c>
-      <c r="H76" s="3">
-        <v>20100</v>
-      </c>
-      <c r="I76" s="3">
-        <v>15600</v>
-      </c>
-      <c r="J76" s="3">
-        <v>21200</v>
+        <v>-27900</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K76" s="3">
         <v>9200</v>
@@ -2638,17 +2640,17 @@
       <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
-        <v>44196</v>
-      </c>
-      <c r="H80" s="2">
-        <v>43830</v>
-      </c>
-      <c r="I80" s="2">
-        <v>43465</v>
-      </c>
-      <c r="J80" s="2">
-        <v>43100</v>
+      <c r="G80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K80" s="2">
         <v>42735</v>
@@ -2663,22 +2665,22 @@
         <v>-2200</v>
       </c>
       <c r="E81" s="3">
-        <v>-15600</v>
+        <v>-5800</v>
       </c>
       <c r="F81" s="3">
-        <v>-24100</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-16100</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-11800</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-26600</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-2600</v>
+        <v>-4100</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K81" s="3">
         <v>-18000</v>
@@ -2706,23 +2708,23 @@
       <c r="D83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>100</v>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -2887,22 +2889,22 @@
         <v>-7400</v>
       </c>
       <c r="E89" s="3">
-        <v>-15000</v>
+        <v>-2600</v>
       </c>
       <c r="F89" s="3">
-        <v>-14500</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-13600</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-9900</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-10800</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-12300</v>
+        <v>-4100</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K89" s="3">
         <v>-10800</v>
@@ -2942,11 +2944,11 @@
       <c r="H91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-400</v>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3020,11 +3022,11 @@
       <c r="D94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E94" s="3">
-        <v>-12200</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>4</v>
@@ -3032,11 +3034,11 @@
       <c r="H94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-400</v>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K94" s="3">
         <v>8500</v>
@@ -3184,23 +3186,23 @@
       <c r="D100" s="3">
         <v>11100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="E100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F100" s="3">
-        <v>33300</v>
-      </c>
-      <c r="G100" s="3">
-        <v>17900</v>
-      </c>
-      <c r="H100" s="3">
-        <v>16000</v>
-      </c>
-      <c r="I100" s="3">
-        <v>9900</v>
-      </c>
-      <c r="J100" s="3">
-        <v>20100</v>
+        <v>6000</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K100" s="3">
         <v>1800</v>
@@ -3211,26 +3213,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -3245,22 +3247,22 @@
         <v>3700</v>
       </c>
       <c r="E102" s="3">
-        <v>-27200</v>
+        <v>-2600</v>
       </c>
       <c r="F102" s="3">
-        <v>18800</v>
+        <v>1900</v>
       </c>
       <c r="G102" s="3">
-        <v>4300</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
-        <v>6200</v>
+        <v>0</v>
       </c>
       <c r="I102" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
-        <v>7300</v>
+        <v>0</v>
       </c>
       <c r="K102" s="3">
         <v>-400</v>

--- a/AAII_Financials/Yearly/CRVO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CRVO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
   <si>
     <t>CRVO</t>
   </si>
@@ -656,44 +656,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="H7" s="2" t="s">
         <v>4</v>
       </c>
@@ -703,21 +703,24 @@
       <c r="J7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E8" s="3">
         <v>7100</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F8" s="3" t="s">
         <v>4</v>
       </c>
@@ -733,24 +736,27 @@
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E9" s="3">
         <v>8400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1300</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G9" s="3" t="s">
         <v>4</v>
       </c>
@@ -766,20 +772,23 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>-1300</v>
+        <v>-9100</v>
       </c>
       <c r="E10" s="3">
         <v>-1300</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
+      <c r="F10" s="3">
+        <v>-1300</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>4</v>
@@ -796,9 +805,12 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -811,23 +823,24 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E12" s="3">
         <v>8400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2400</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H12" s="3" t="s">
         <v>4</v>
       </c>
@@ -837,12 +850,15 @@
       <c r="J12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L12" s="3">
         <v>7300</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -870,24 +886,27 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>800</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
         <v>-100</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
@@ -900,9 +919,12 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -930,9 +952,12 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -942,23 +967,24 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>14200</v>
+        <v>28000</v>
       </c>
       <c r="E17" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F17" s="3">
         <v>3500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5000</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H17" s="3" t="s">
         <v>4</v>
       </c>
@@ -968,27 +994,30 @@
       <c r="J17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L17" s="3">
         <v>18400</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-7000</v>
+        <v>-18200</v>
       </c>
       <c r="E18" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5000</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H18" s="3" t="s">
         <v>4</v>
       </c>
@@ -998,12 +1027,15 @@
       <c r="J18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="3">
         <v>-18400</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1016,23 +1048,24 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-700</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>4</v>
       </c>
@@ -1042,27 +1075,30 @@
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1600</v>
+        <v>-18200</v>
       </c>
       <c r="E21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-5900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-4300</v>
       </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
       <c r="H21" s="3">
         <v>0</v>
       </c>
@@ -1072,26 +1108,29 @@
       <c r="J21" s="3">
         <v>0</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>4</v>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>4</v>
@@ -1102,27 +1141,30 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4100</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H23" s="3" t="s">
         <v>4</v>
       </c>
@@ -1132,12 +1174,15 @@
       <c r="J23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L23" s="3">
         <v>-18400</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1162,12 +1207,15 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3">
         <v>-400</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1195,24 +1243,27 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4100</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H26" s="3" t="s">
         <v>4</v>
       </c>
@@ -1222,27 +1273,30 @@
       <c r="J26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L26" s="3">
         <v>-18000</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4100</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H27" s="3" t="s">
         <v>4</v>
       </c>
@@ -1252,12 +1306,15 @@
       <c r="J27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L27" s="3">
         <v>-18000</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1285,9 +1342,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1312,12 +1372,15 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1345,9 +1408,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1375,24 +1441,27 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>5400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>700</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>4</v>
       </c>
@@ -1402,27 +1471,30 @@
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4100</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H33" s="3" t="s">
         <v>4</v>
       </c>
@@ -1432,12 +1504,15 @@
       <c r="J33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L33" s="3">
         <v>-18000</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1465,24 +1540,27 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4100</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H35" s="3" t="s">
         <v>4</v>
       </c>
@@ -1492,32 +1570,35 @@
       <c r="J35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L35" s="3">
         <v>-18000</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="H38" s="2" t="s">
         <v>4</v>
       </c>
@@ -1527,12 +1608,15 @@
       <c r="J38" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K38" s="2">
+      <c r="K38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1545,8 +1629,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1559,23 +1644,24 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E41" s="3">
         <v>7800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6700</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H41" s="3" t="s">
         <v>4</v>
       </c>
@@ -1585,17 +1671,20 @@
       <c r="J41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L41" s="3">
         <v>1600</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>29900</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -1615,27 +1704,30 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E43" s="3">
         <v>900</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3">
         <v>100</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>4</v>
       </c>
@@ -1645,12 +1737,15 @@
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1675,12 +1770,15 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1690,12 +1788,12 @@
       <c r="E45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>4</v>
       </c>
@@ -1705,27 +1803,30 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E46" s="3">
         <v>10000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6800</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H46" s="3" t="s">
         <v>4</v>
       </c>
@@ -1735,12 +1836,15 @@
       <c r="J46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L46" s="3">
         <v>1600</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1765,12 +1869,15 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1795,12 +1902,15 @@
       <c r="J48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L48" s="3">
         <v>100</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1813,8 +1923,8 @@
       <c r="F49" s="3">
         <v>0</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>4</v>
+      <c r="G49" s="3">
+        <v>0</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>4</v>
@@ -1825,12 +1935,15 @@
       <c r="J49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K49" s="3">
+      <c r="K49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L49" s="3">
         <v>15600</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1858,9 +1971,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1888,17 +2004,20 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>4</v>
+      <c r="D52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>4</v>
@@ -1915,12 +2034,15 @@
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1948,24 +2070,27 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E54" s="3">
         <v>10000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6800</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H54" s="3" t="s">
         <v>4</v>
       </c>
@@ -1975,12 +2100,15 @@
       <c r="J54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L54" s="3">
         <v>17500</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1993,8 +2121,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2007,22 +2136,23 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
         <v>700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>100</v>
       </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
+      <c r="G57" s="3">
+        <v>0</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>4</v>
@@ -2033,12 +2163,15 @@
       <c r="J57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L57" s="3">
         <v>1700</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2046,14 +2179,14 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>12400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4100</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H58" s="3" t="s">
         <v>4</v>
       </c>
@@ -2063,12 +2196,15 @@
       <c r="J58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K58" s="3">
+      <c r="K58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L58" s="3">
         <v>1900</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2079,10 +2215,10 @@
         <v>100</v>
       </c>
       <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>4</v>
@@ -2093,27 +2229,30 @@
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3">
         <v>900</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E60" s="3">
         <v>2600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4600</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H60" s="3" t="s">
         <v>4</v>
       </c>
@@ -2123,12 +2262,15 @@
       <c r="J60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L60" s="3">
         <v>4400</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2139,11 +2281,11 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>5900</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -2154,11 +2296,14 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>600</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2183,12 +2328,15 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3">
         <v>3300</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2216,9 +2364,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2246,9 +2397,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2276,24 +2430,27 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E66" s="3">
         <v>2600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10500</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H66" s="3" t="s">
         <v>4</v>
       </c>
@@ -2303,12 +2460,15 @@
       <c r="J66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L66" s="3">
         <v>8300</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2321,8 +2481,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2350,9 +2511,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2380,9 +2544,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2390,13 +2557,13 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
-        <v>24300</v>
+        <v>0</v>
       </c>
       <c r="F70" s="3">
         <v>24300</v>
       </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>24300</v>
       </c>
       <c r="H70" s="3">
         <v>0</v>
@@ -2410,9 +2577,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2440,24 +2610,27 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-70700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-54400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-52300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-46500</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H72" s="3" t="s">
         <v>4</v>
       </c>
@@ -2467,12 +2640,15 @@
       <c r="J72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>-60200</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2500,9 +2676,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2530,9 +2709,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2560,24 +2742,27 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E76" s="3">
         <v>7400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-33300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-27900</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H76" s="3" t="s">
         <v>4</v>
       </c>
@@ -2587,12 +2772,15 @@
       <c r="J76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L76" s="3">
         <v>9200</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2620,29 +2808,32 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="H80" s="2" t="s">
         <v>4</v>
       </c>
@@ -2652,27 +2843,30 @@
       <c r="J80" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K80" s="2">
+      <c r="K80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4100</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H81" s="3" t="s">
         <v>4</v>
       </c>
@@ -2682,12 +2876,15 @@
       <c r="J81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L81" s="3">
         <v>-18000</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2700,8 +2897,9 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2726,12 +2924,15 @@
       <c r="J83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2759,9 +2960,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2789,9 +2993,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2819,9 +3026,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2849,9 +3059,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2879,24 +3092,27 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4100</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H89" s="3" t="s">
         <v>4</v>
       </c>
@@ -2906,12 +3122,15 @@
       <c r="J89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L89" s="3">
         <v>-10800</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2924,8 +3143,9 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -2950,12 +3170,15 @@
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2983,9 +3206,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3013,14 +3239,17 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>4</v>
+      <c r="D94" s="3">
+        <v>-28700</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>4</v>
@@ -3040,12 +3269,15 @@
       <c r="J94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L94" s="3">
         <v>8500</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3058,8 +3290,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3087,9 +3320,12 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3117,9 +3353,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3147,9 +3386,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3177,24 +3419,27 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>46400</v>
+      </c>
+      <c r="E100" s="3">
         <v>11100</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G100" s="3">
         <v>6000</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H100" s="3" t="s">
         <v>4</v>
       </c>
@@ -3204,12 +3449,15 @@
       <c r="J100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L100" s="3">
         <v>1800</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3234,27 +3482,30 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E102" s="3">
         <v>3700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1900</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
         <v>0</v>
       </c>
@@ -3265,9 +3516,12 @@
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-400</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CRVO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CRVO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="92">
   <si>
     <t>CRVO</t>
   </si>
@@ -656,47 +656,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="I7" s="2" t="s">
         <v>4</v>
       </c>
@@ -706,24 +706,27 @@
       <c r="K7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E8" s="3">
         <v>9700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7100</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G8" s="3" t="s">
         <v>4</v>
       </c>
@@ -739,27 +742,30 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E9" s="3">
         <v>18800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1300</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H9" s="3" t="s">
         <v>4</v>
       </c>
@@ -775,23 +781,26 @@
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E10" s="3">
         <v>-9100</v>
-      </c>
-      <c r="E10" s="3">
-        <v>-1300</v>
       </c>
       <c r="F10" s="3">
         <v>-1300</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
+      <c r="G10" s="3">
+        <v>-1300</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>4</v>
@@ -808,9 +817,12 @@
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -824,26 +836,27 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E12" s="3">
         <v>18800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2400</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I12" s="3" t="s">
         <v>4</v>
       </c>
@@ -853,12 +866,15 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3">
         <v>7300</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -889,9 +905,12 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -904,12 +923,12 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
         <v>-100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
@@ -922,9 +941,12 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -955,9 +977,12 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -968,26 +993,27 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E17" s="3">
         <v>28000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5000</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I17" s="3" t="s">
         <v>4</v>
       </c>
@@ -997,30 +1023,33 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" s="3">
         <v>18400</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-18200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-7800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5000</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1030,12 +1059,15 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3">
         <v>-18400</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1049,8 +1081,9 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1058,17 +1091,17 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-5400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-700</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>4</v>
       </c>
@@ -1078,30 +1111,33 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-18200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4300</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
       <c r="I21" s="3">
         <v>0</v>
       </c>
@@ -1111,12 +1147,15 @@
       <c r="K21" s="3">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1126,14 +1165,14 @@
       <c r="E22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>4</v>
+      <c r="H22" s="3">
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>4</v>
@@ -1144,30 +1183,33 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-16300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4100</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I23" s="3" t="s">
         <v>4</v>
       </c>
@@ -1177,12 +1219,15 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="3">
         <v>-18400</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1210,12 +1255,15 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1246,27 +1294,30 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-16300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4100</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I26" s="3" t="s">
         <v>4</v>
       </c>
@@ -1276,30 +1327,33 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="3">
         <v>-18000</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-16300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4100</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I27" s="3" t="s">
         <v>4</v>
       </c>
@@ -1309,12 +1363,15 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" s="3">
         <v>-18000</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1345,9 +1402,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1375,12 +1435,15 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1411,9 +1474,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1444,9 +1510,12 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1454,17 +1523,17 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>5400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>700</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>4</v>
       </c>
@@ -1474,30 +1543,33 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-16300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4100</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I33" s="3" t="s">
         <v>4</v>
       </c>
@@ -1507,12 +1579,15 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="3">
         <v>-18000</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1543,27 +1618,30 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-16300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4100</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I35" s="3" t="s">
         <v>4</v>
       </c>
@@ -1573,35 +1651,38 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M35" s="3">
         <v>-18000</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="I38" s="2" t="s">
         <v>4</v>
       </c>
@@ -1611,12 +1692,15 @@
       <c r="K38" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="L38" s="2">
+      <c r="L38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1630,8 +1714,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1645,26 +1730,27 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E41" s="3">
         <v>9000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6700</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>4</v>
       </c>
@@ -1674,21 +1760,24 @@
       <c r="K41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M41" s="3">
         <v>1600</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E42" s="3">
         <v>29900</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
@@ -1707,30 +1796,33 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400</v>
+      </c>
+      <c r="E43" s="3">
         <v>2300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>900</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>4</v>
       </c>
@@ -1740,12 +1832,15 @@
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1773,17 +1868,20 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
+      <c r="D45" s="3">
+        <v>300</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>4</v>
@@ -1791,12 +1889,12 @@
       <c r="F45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>4</v>
       </c>
@@ -1806,30 +1904,33 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E46" s="3">
         <v>43100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6800</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>4</v>
       </c>
@@ -1839,12 +1940,15 @@
       <c r="K46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M46" s="3">
         <v>1600</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1872,12 +1976,15 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1905,12 +2012,15 @@
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M48" s="3">
         <v>100</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1926,8 +2036,8 @@
       <c r="G49" s="3">
         <v>0</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>4</v>
+      <c r="H49" s="3">
+        <v>0</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>4</v>
@@ -1938,12 +2048,15 @@
       <c r="K49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L49" s="3">
+      <c r="L49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M49" s="3">
         <v>15600</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1974,9 +2087,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2007,20 +2123,23 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>4</v>
@@ -2037,12 +2156,15 @@
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M52" s="3">
         <v>200</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2073,27 +2195,30 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E54" s="3">
         <v>43100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6800</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2103,12 +2228,15 @@
       <c r="K54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M54" s="3">
         <v>17500</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2122,8 +2250,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2137,8 +2266,9 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2146,16 +2276,16 @@
         <v>1500</v>
       </c>
       <c r="E57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F57" s="3">
         <v>700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>100</v>
       </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
+      <c r="H57" s="3">
+        <v>0</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>4</v>
@@ -2166,12 +2296,15 @@
       <c r="K57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M57" s="3">
         <v>1700</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2182,14 +2315,14 @@
         <v>0</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>12400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4100</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>4</v>
       </c>
@@ -2199,12 +2332,15 @@
       <c r="K58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L58" s="3">
+      <c r="L58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M58" s="3">
         <v>1900</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2218,10 +2354,10 @@
         <v>100</v>
       </c>
       <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="H59" s="3">
+        <v>0</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>4</v>
@@ -2232,30 +2368,33 @@
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>900</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E60" s="3">
         <v>3900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4600</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>4</v>
       </c>
@@ -2265,12 +2404,15 @@
       <c r="K60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M60" s="3">
         <v>4400</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2284,11 +2426,11 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>5900</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2299,11 +2441,14 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>600</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2331,12 +2476,15 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>3300</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2367,9 +2515,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2400,9 +2551,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2433,27 +2587,30 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E66" s="3">
         <v>3900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10500</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>4</v>
       </c>
@@ -2463,12 +2620,15 @@
       <c r="K66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M66" s="3">
         <v>8300</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2482,8 +2642,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2514,9 +2675,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2547,9 +2711,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2560,13 +2727,13 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>24300</v>
+        <v>0</v>
       </c>
       <c r="G70" s="3">
         <v>24300</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>24300</v>
       </c>
       <c r="I70" s="3">
         <v>0</v>
@@ -2580,9 +2747,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2613,27 +2783,30 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-97700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-70700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-54400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-52300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-46500</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>4</v>
       </c>
@@ -2643,12 +2816,15 @@
       <c r="K72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
         <v>-60200</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2679,9 +2855,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2712,9 +2891,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2745,27 +2927,30 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E76" s="3">
         <v>39200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-33300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-27900</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>4</v>
       </c>
@@ -2775,12 +2960,15 @@
       <c r="K76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M76" s="3">
         <v>9200</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2811,32 +2999,35 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="I80" s="2" t="s">
         <v>4</v>
       </c>
@@ -2846,30 +3037,33 @@
       <c r="K80" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="L80" s="2">
+      <c r="L80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-16300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4100</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I81" s="3" t="s">
         <v>4</v>
       </c>
@@ -2879,12 +3073,15 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M81" s="3">
         <v>-18000</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2898,8 +3095,9 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2927,12 +3125,15 @@
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2963,9 +3164,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2996,9 +3200,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3029,9 +3236,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3062,9 +3272,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3095,27 +3308,30 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-16500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4100</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I89" s="3" t="s">
         <v>4</v>
       </c>
@@ -3125,12 +3341,15 @@
       <c r="K89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M89" s="3">
         <v>-10800</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3144,8 +3363,9 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3173,12 +3393,15 @@
       <c r="K91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3209,9 +3432,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3242,18 +3468,21 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-28700</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F94" s="3" t="s">
         <v>4</v>
       </c>
@@ -3272,12 +3501,15 @@
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M94" s="3">
         <v>8500</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3291,8 +3523,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3323,9 +3556,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3356,9 +3592,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3389,9 +3628,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3422,27 +3664,30 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E100" s="3">
         <v>46400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>11100</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H100" s="3">
         <v>6000</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>4</v>
       </c>
@@ -3452,12 +3697,15 @@
       <c r="K100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M100" s="3">
         <v>1800</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3485,30 +3733,33 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E102" s="3">
         <v>1200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1900</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
@@ -3519,9 +3770,12 @@
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-400</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
